--- a/output/pdf_financials_xlsx/PEZM.H.xlsx
+++ b/output/pdf_financials_xlsx/PEZM.H.xlsx
@@ -1107,13 +1107,13 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.026013</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.05404</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.029896</v>
       </c>
     </row>
     <row r="13">
@@ -2105,13 +2105,13 @@
         <v>-0.223272</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.233733</v>
+        <v>-0.259746</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.11751</v>
+        <v>-0.17155</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.143967</v>
+        <v>-0.173863</v>
       </c>
     </row>
     <row r="28">
@@ -2229,13 +2229,13 @@
         <v>-0.223272</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.233733</v>
+        <v>-0.259746</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.11751</v>
+        <v>-0.17155</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.143967</v>
+        <v>-0.173863</v>
       </c>
     </row>
     <row r="30">
@@ -2498,43 +2498,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000433</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.00598</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.003772</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.2e-05</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.00072</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000507</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.003622</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.001801</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.001918</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.074624</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>4.2e-05</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.377697</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>1.368822</v>
@@ -2614,43 +2614,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000433</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.00598</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.003772</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.2e-05</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.00072</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000507</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.003622</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.001801</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.001918</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.074624</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>4.2e-05</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.377697</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>1.368822</v>
@@ -3310,37 +3310,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.001746</v>
+        <v>0.001313</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.009051</v>
+        <v>0.003071</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.006882</v>
+        <v>0.00311</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.003067</v>
+        <v>0.003035</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.001195</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.002203</v>
+        <v>0.001483</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.002146</v>
+        <v>0.001639</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.006077</v>
+        <v>0.002455</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.00255</v>
+        <v>0.000749</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.002397</v>
+        <v>0.000479</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.077226</v>
+        <v>0.002602</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
@@ -22744,7 +22744,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -23641,7 +23641,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">

--- a/output/pdf_financials_xlsx/PEZM.H.xlsx
+++ b/output/pdf_financials_xlsx/PEZM.H.xlsx
@@ -794,16 +794,16 @@
         <v>0.032924</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.039783</v>
+        <v>0.172593</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.044495</v>
+        <v>0.195197</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.045094</v>
+        <v>0.143485</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.046016</v>
+        <v>0.134389</v>
       </c>
     </row>
     <row r="8">
@@ -980,16 +980,16 @@
         <v>0.032924</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.039783</v>
+        <v>0.172593</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.044495</v>
+        <v>0.195197</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.045094</v>
+        <v>0.143485</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.046016</v>
+        <v>0.134389</v>
       </c>
     </row>
     <row r="11">
@@ -1051,7 +1051,7 @@
         <v>-0.17155</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.046016</v>
+        <v>-0.134389</v>
       </c>
     </row>
     <row r="12">
@@ -4359,10 +4359,10 @@
         <v>0</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.032682</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.14347</v>
       </c>
       <c r="Q64" s="3" t="n">
         <v>0</v>
@@ -4591,7 +4591,7 @@
         <v>0</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0</v>
+        <v>0.032682</v>
       </c>
       <c r="P68" s="3" t="n">
         <v>0.14347</v>
@@ -9909,7 +9909,11 @@
           <t>Accounts payable – Note 4 $</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AccountsPayable</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -21925,7 +21929,11 @@
           <t>Consulting fees – Note 4 $</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -22103,7 +22111,11 @@
           <t>Management fees – Note 4</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -22198,7 +22210,11 @@
           <t>Office and general – Note 4</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -22544,7 +22560,11 @@
           <t>Travel – Note 4</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PEZM.H.xlsx
+++ b/output/pdf_financials_xlsx/PEZM.H.xlsx
@@ -16511,7 +16511,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
